--- a/packages/calculators/src/modules/test/6.4-crop-burning.xlsx
+++ b/packages/calculators/src/modules/test/6.4-crop-burning.xlsx
@@ -1,20 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10817"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/eddiesholl/Code/aginnovationaustralia/emissions-calculators-internal/packages/calculators/src/modules/test/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{878BA584-F001-1D47-9BC5-3F8D0D685864}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A726506-1298-3344-8C99-5DD78FF866AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20" yWindow="660" windowWidth="28800" windowHeight="15940" xr2:uid="{5678E890-3691-CF46-80E7-00FB1F103661}"/>
   </bookViews>
   <sheets>
     <sheet name="6.4.1.1" sheetId="3" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -648,6 +646,34 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="common"/>
+    </sheetNames>
+    <definedNames>
+      <definedName name="common_cch4" refersTo="='common'!$B$3"/>
+      <definedName name="common_cn2o" refersTo="='common'!$B$4"/>
+    </definedNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="3">
+          <cell r="B3">
+            <v>1.33</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>1.57</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1078,7 +1104,7 @@
         <v>11000</v>
       </c>
       <c r="D5" s="12">
-        <f>IF(ISBLANK(A5), "", VLOOKUP($A5, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" ref="D5:D22" si="0">IF(ISBLANK(A5), "", VLOOKUP($A5, $Q$22:$Y$39, 2, FALSE))</f>
         <v>0.25</v>
       </c>
       <c r="E5" s="12">
@@ -1102,7 +1128,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J5">
-        <f>IF(ISBLANK(A5),"", (C5*D5*F5*G5*H5*B5))</f>
+        <f t="shared" ref="J5:J22" si="1">IF(ISBLANK(A5),"", (C5*D5*F5*G5*H5*B5))</f>
         <v>88</v>
       </c>
       <c r="K5">
@@ -1115,15 +1141,15 @@
       </c>
       <c r="M5">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N5">
         <f>IF(ISBLANK(#REF!), "", J5*K5*L5*M5/1000)</f>
-        <v>1.6426666666666668E-4</v>
+        <v>1.6385600000000004E-4</v>
       </c>
       <c r="O5">
         <f>J5*I5*$R$9*$R$8/1000</f>
-        <v>5.2548571428571423E-6</v>
+        <v>5.2500800000000011E-6</v>
       </c>
     </row>
     <row r="6" spans="1:19">
@@ -1137,7 +1163,7 @@
         <v>12000</v>
       </c>
       <c r="D6" s="12">
-        <f>IF(ISBLANK(A6), "", VLOOKUP($A6, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.25</v>
       </c>
       <c r="E6" s="12">
@@ -1145,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="12">
-        <f t="shared" ref="F6:F22" si="0">IF(E6="n/a", 0, E6)</f>
+        <f t="shared" ref="F6:F22" si="2">IF(E6="n/a", 0, E6)</f>
         <v>1</v>
       </c>
       <c r="G6" s="12">
@@ -1161,7 +1187,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J6">
-        <f>IF(ISBLANK(A6),"", (C6*D6*F6*G6*H6*B6))</f>
+        <f t="shared" si="1"/>
         <v>192</v>
       </c>
       <c r="K6">
@@ -1174,22 +1200,22 @@
       </c>
       <c r="M6">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N6">
         <f>IF(ISBLANK(#REF!), "", J6*K6*L6*M6/1000)</f>
-        <v>3.5840000000000004E-4</v>
+        <v>3.5750400000000002E-4</v>
       </c>
       <c r="O6">
-        <f t="shared" ref="O6:O22" si="1">J6*I6*$R$9*$R$8/1000</f>
-        <v>1.1465142857142856E-5</v>
+        <f t="shared" ref="O6:O22" si="3">J6*I6*$R$9*$R$8/1000</f>
+        <v>1.145472E-5</v>
       </c>
       <c r="Q6" t="s">
         <v>43</v>
       </c>
       <c r="R6">
-        <f>16/12</f>
-        <v>1.3333333333333333</v>
+        <f>[1]!common_cch4</f>
+        <v>1.33</v>
       </c>
     </row>
     <row r="7" spans="1:19">
@@ -1203,7 +1229,7 @@
         <v>13000</v>
       </c>
       <c r="D7" s="12">
-        <f>IF(ISBLANK(A7), "", VLOOKUP($A7, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.31</v>
       </c>
       <c r="E7" s="12">
@@ -1211,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G7" s="12">
@@ -1227,7 +1253,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J7">
-        <f>IF(ISBLANK(A7),"", (C7*D7*F7*G7*H7*B7))</f>
+        <f t="shared" si="1"/>
         <v>2179.84</v>
       </c>
       <c r="K7">
@@ -1240,15 +1266,15 @@
       </c>
       <c r="M7">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N7">
         <f>IF(ISBLANK(#REF!), "", J7*K7*L7*M7/1000)</f>
-        <v>4.2724864E-3</v>
+        <v>4.2618051840000006E-3</v>
       </c>
       <c r="O7">
-        <f t="shared" si="1"/>
-        <v>1.82234624E-4</v>
+        <f t="shared" si="3"/>
+        <v>1.8206895616000002E-4</v>
       </c>
       <c r="Q7" t="s">
         <v>44</v>
@@ -1268,7 +1294,7 @@
         <v>14000</v>
       </c>
       <c r="D8" s="12">
-        <f>IF(ISBLANK(A8), "", VLOOKUP($A8, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.31</v>
       </c>
       <c r="E8" s="12">
@@ -1276,7 +1302,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G8" s="12">
@@ -1292,7 +1318,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J8">
-        <f>IF(ISBLANK(A8),"", (C8*D8*F8*G8*H8*B8))</f>
+        <f t="shared" si="1"/>
         <v>4695.04</v>
       </c>
       <c r="K8">
@@ -1305,22 +1331,22 @@
       </c>
       <c r="M8">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N8">
         <f>IF(ISBLANK(#REF!), "", J8*K8*L8*M8/1000)</f>
-        <v>9.2022783999999996E-3</v>
+        <v>9.1792727040000011E-3</v>
       </c>
       <c r="O8">
-        <f t="shared" si="1"/>
-        <v>3.92505344E-4</v>
+        <f t="shared" si="3"/>
+        <v>3.9214852095999995E-4</v>
       </c>
       <c r="Q8" s="2" t="s">
         <v>2</v>
       </c>
       <c r="R8">
-        <f>44/28</f>
-        <v>1.5714285714285714</v>
+        <f>[1]!common_cn2o</f>
+        <v>1.57</v>
       </c>
     </row>
     <row r="9" spans="1:19">
@@ -1334,7 +1360,7 @@
         <v>15000</v>
       </c>
       <c r="D9" s="12">
-        <f>IF(ISBLANK(A9), "", VLOOKUP($A9, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="E9" s="12" t="str">
@@ -1342,7 +1368,7 @@
         <v>n/a</v>
       </c>
       <c r="F9" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G9" s="12">
@@ -1358,7 +1384,7 @@
         <v>0.02</v>
       </c>
       <c r="J9">
-        <f>IF(ISBLANK(A9),"", (C9*D9*F9*G9*H9*B9))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K9">
@@ -1371,14 +1397,14 @@
       </c>
       <c r="M9">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N9">
         <f>IF(ISBLANK(#REF!), "", J9*K9*L9*M9/1000)</f>
         <v>0</v>
       </c>
       <c r="O9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q9" s="2" t="s">
@@ -1399,7 +1425,7 @@
         <v>16000</v>
       </c>
       <c r="D10" s="12">
-        <f>IF(ISBLANK(A10), "", VLOOKUP($A10, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.34</v>
       </c>
       <c r="E10" s="12" t="str">
@@ -1407,7 +1433,7 @@
         <v>n/a</v>
       </c>
       <c r="F10" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G10" s="12">
@@ -1423,7 +1449,7 @@
         <v>0.02</v>
       </c>
       <c r="J10">
-        <f>IF(ISBLANK(A10),"", (C10*D10*F10*G10*H10*B10))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K10">
@@ -1436,14 +1462,14 @@
       </c>
       <c r="M10">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N10">
         <f>IF(ISBLANK(#REF!), "", J10*K10*L10*M10/1000)</f>
         <v>0</v>
       </c>
       <c r="O10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1458,7 +1484,7 @@
         <v>17000</v>
       </c>
       <c r="D11" s="12">
-        <f>IF(ISBLANK(A11), "", VLOOKUP($A11, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.9</v>
       </c>
       <c r="E11" s="12" t="str">
@@ -1466,7 +1492,7 @@
         <v>n/a</v>
       </c>
       <c r="F11" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G11" s="12">
@@ -1482,7 +1508,7 @@
         <v>0.01</v>
       </c>
       <c r="J11">
-        <f>IF(ISBLANK(A11),"", (C11*D11*F11*G11*H11*B11))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K11">
@@ -1495,14 +1521,14 @@
       </c>
       <c r="M11">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N11">
         <f>IF(ISBLANK(#REF!), "", J11*K11*L11*M11/1000)</f>
         <v>0</v>
       </c>
       <c r="O11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q11" s="2"/>
@@ -1519,7 +1545,7 @@
         <v>18000</v>
       </c>
       <c r="D12" s="12">
-        <f>IF(ISBLANK(A12), "", VLOOKUP($A12, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="E12" s="12" t="str">
@@ -1527,7 +1553,7 @@
         <v>n/a</v>
       </c>
       <c r="F12" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G12" s="12">
@@ -1543,7 +1569,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J12">
-        <f>IF(ISBLANK(A12),"", (C12*D12*F12*G12*H12*B12))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K12">
@@ -1556,14 +1582,14 @@
       </c>
       <c r="M12">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N12">
         <f>IF(ISBLANK(#REF!), "", J12*K12*L12*M12/1000)</f>
         <v>0</v>
       </c>
       <c r="O12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="Q12" s="2"/>
@@ -1580,7 +1606,7 @@
         <v>19000</v>
       </c>
       <c r="D13" s="12">
-        <f>IF(ISBLANK(A13), "", VLOOKUP($A13, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.34</v>
       </c>
       <c r="E13" s="12" t="str">
@@ -1588,7 +1614,7 @@
         <v>n/a</v>
       </c>
       <c r="F13" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="G13" s="12">
@@ -1604,7 +1630,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J13">
-        <f>IF(ISBLANK(A13),"", (C13*D13*F13*G13*H13*B13))</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="K13">
@@ -1617,14 +1643,14 @@
       </c>
       <c r="M13">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N13">
         <f>IF(ISBLANK(#REF!), "", J13*K13*L13*M13/1000)</f>
         <v>0</v>
       </c>
       <c r="O13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -1639,7 +1665,7 @@
         <v>20000</v>
       </c>
       <c r="D14" s="12">
-        <f>IF(ISBLANK(A14), "", VLOOKUP($A14, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.07</v>
       </c>
       <c r="E14" s="12">
@@ -1647,7 +1673,7 @@
         <v>0.5</v>
       </c>
       <c r="F14" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G14" s="12">
@@ -1663,7 +1689,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="J14">
-        <f>IF(ISBLANK(A14),"", (C14*D14*F14*G14*H14*B14))</f>
+        <f t="shared" si="1"/>
         <v>2182.7999999999997</v>
       </c>
       <c r="K14">
@@ -1676,15 +1702,15 @@
       </c>
       <c r="M14">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N14">
         <f>IF(ISBLANK(#REF!), "", J14*K14*L14*M14/1000)</f>
-        <v>4.278287999999999E-3</v>
+        <v>4.2675922799999995E-3</v>
       </c>
       <c r="O14">
-        <f t="shared" si="1"/>
-        <v>4.1710189714285704E-4</v>
+        <f t="shared" si="3"/>
+        <v>4.1672271359999996E-4</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" s="2"/>
@@ -1701,7 +1727,7 @@
         <v>21000</v>
       </c>
       <c r="D15" s="12">
-        <f>IF(ISBLANK(A15), "", VLOOKUP($A15, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>2.08</v>
       </c>
       <c r="E15" s="12">
@@ -1709,7 +1735,7 @@
         <v>0.5</v>
       </c>
       <c r="F15" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G15" s="12">
@@ -1725,7 +1751,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="J15">
-        <f>IF(ISBLANK(A15),"", (C15*D15*F15*G15*H15*B15))</f>
+        <f t="shared" si="1"/>
         <v>5346.4319999999998</v>
       </c>
       <c r="K15">
@@ -1738,15 +1764,15 @@
       </c>
       <c r="M15">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N15">
         <f>IF(ISBLANK(#REF!), "", J15*K15*L15*M15/1000)</f>
-        <v>9.980006399999998E-3</v>
+        <v>9.9550563840000005E-3</v>
       </c>
       <c r="O15">
-        <f t="shared" si="1"/>
-        <v>5.7466506239999991E-4</v>
+        <f t="shared" si="3"/>
+        <v>5.7414263961599995E-4</v>
       </c>
       <c r="Q15" s="2"/>
       <c r="R15" s="2"/>
@@ -1763,7 +1789,7 @@
         <v>22000</v>
       </c>
       <c r="D16" s="12">
-        <f>IF(ISBLANK(A16), "", VLOOKUP($A16, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.24</v>
       </c>
       <c r="E16" s="12">
@@ -1771,7 +1797,7 @@
         <v>0.5</v>
       </c>
       <c r="F16" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G16" s="12">
@@ -1787,7 +1813,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J16">
-        <f>IF(ISBLANK(A16),"", (C16*D16*F16*G16*H16*B16))</f>
+        <f t="shared" si="1"/>
         <v>3060.8160000000003</v>
       </c>
       <c r="K16">
@@ -1800,15 +1826,15 @@
       </c>
       <c r="M16">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N16">
         <f>IF(ISBLANK(#REF!), "", J16*K16*L16*M16/1000)</f>
-        <v>5.7135232000000008E-3</v>
+        <v>5.6992393920000011E-3</v>
       </c>
       <c r="O16">
-        <f t="shared" si="1"/>
-        <v>2.5588421760000004E-4</v>
+        <f t="shared" si="3"/>
+        <v>2.55651595584E-4</v>
       </c>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
@@ -1825,7 +1851,7 @@
         <v>23000</v>
       </c>
       <c r="D17" s="12">
-        <f>IF(ISBLANK(A17), "", VLOOKUP($A17, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>0.81</v>
       </c>
       <c r="E17" s="12">
@@ -1833,7 +1859,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>1</v>
       </c>
       <c r="G17" s="12">
@@ -1849,7 +1875,7 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J17">
-        <f>IF(ISBLANK(A17),"", (C17*D17*F17*G17*H17*B17))</f>
+        <f t="shared" si="1"/>
         <v>3800.5200000000004</v>
       </c>
       <c r="K17">
@@ -1862,15 +1888,15 @@
       </c>
       <c r="M17">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N17">
         <f>IF(ISBLANK(#REF!), "", J17*K17*L17*M17/1000)</f>
-        <v>7.4490192000000004E-3</v>
+        <v>7.4303966520000014E-3</v>
       </c>
       <c r="O17">
-        <f t="shared" si="1"/>
-        <v>2.2694533714285713E-4</v>
+        <f t="shared" si="3"/>
+        <v>2.2673902320000003E-4</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -1884,7 +1910,7 @@
         <v>24000</v>
       </c>
       <c r="D18" s="12">
-        <f>IF(ISBLANK(A18), "", VLOOKUP($A18, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.42</v>
       </c>
       <c r="E18" s="12">
@@ -1892,7 +1918,7 @@
         <v>0.5</v>
       </c>
       <c r="F18" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G18" s="12">
@@ -1908,7 +1934,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J18">
-        <f>IF(ISBLANK(A18),"", (C18*D18*F18*G18*H18*B18))</f>
+        <f t="shared" si="1"/>
         <v>3823.7759999999998</v>
       </c>
       <c r="K18">
@@ -1921,15 +1947,15 @@
       </c>
       <c r="M18">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N18">
         <f>IF(ISBLANK(#REF!), "", J18*K18*L18*M18/1000)</f>
-        <v>7.1377152000000003E-3</v>
+        <v>7.1198709120000011E-3</v>
       </c>
       <c r="O18">
-        <f t="shared" si="1"/>
-        <v>2.7400086308571427E-4</v>
+        <f t="shared" si="3"/>
+        <v>2.73751771392E-4</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
@@ -1945,7 +1971,7 @@
         <v>25000</v>
       </c>
       <c r="D19" s="12">
-        <f>IF(ISBLANK(A19), "", VLOOKUP($A19, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.24</v>
       </c>
       <c r="E19" s="12">
@@ -1953,7 +1979,7 @@
         <v>0.5</v>
       </c>
       <c r="F19" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G19" s="12">
@@ -1969,7 +1995,7 @@
         <v>7.0000000000000001E-3</v>
       </c>
       <c r="J19">
-        <f>IF(ISBLANK(A19),"", (C19*D19*F19*G19*H19*B19))</f>
+        <f t="shared" si="1"/>
         <v>3478.2</v>
       </c>
       <c r="K19">
@@ -1982,15 +2008,15 @@
       </c>
       <c r="M19">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N19">
         <f>IF(ISBLANK(#REF!), "", J19*K19*L19*M19/1000)</f>
-        <v>6.49264E-3</v>
+        <v>6.4764084000000005E-3</v>
       </c>
       <c r="O19">
-        <f t="shared" si="1"/>
-        <v>2.9077752000000002E-4</v>
+        <f t="shared" si="3"/>
+        <v>2.9051317679999999E-4</v>
       </c>
       <c r="Q19" s="2"/>
       <c r="R19" s="2"/>
@@ -2006,7 +2032,7 @@
         <v>26000</v>
       </c>
       <c r="D20" s="12">
-        <f>IF(ISBLANK(A20), "", VLOOKUP($A20, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="E20" s="12">
@@ -2014,7 +2040,7 @@
         <v>0.5</v>
       </c>
       <c r="F20" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G20" s="12">
@@ -2030,7 +2056,7 @@
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="J20">
-        <f>IF(ISBLANK(A20),"", (C20*D20*F20*G20*H20*B20))</f>
+        <f t="shared" si="1"/>
         <v>3978</v>
       </c>
       <c r="K20">
@@ -2043,15 +2069,15 @@
       </c>
       <c r="M20">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N20">
         <f>IF(ISBLANK(#REF!), "", J20*K20*L20*M20/1000)</f>
-        <v>7.4256000000000001E-3</v>
+        <v>7.4070360000000005E-3</v>
       </c>
       <c r="O20">
-        <f t="shared" si="1"/>
-        <v>3.8006948571428571E-4</v>
+        <f t="shared" si="3"/>
+        <v>3.7972396800000003E-4</v>
       </c>
       <c r="Q20" s="2" t="s">
         <v>21</v>
@@ -2070,7 +2096,7 @@
         <v>27000</v>
       </c>
       <c r="D21" s="12">
-        <f>IF(ISBLANK(A21), "", VLOOKUP($A21, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.5</v>
       </c>
       <c r="E21" s="12">
@@ -2078,7 +2104,7 @@
         <v>0.5</v>
       </c>
       <c r="F21" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G21" s="12">
@@ -2094,7 +2120,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J21">
-        <f>IF(ISBLANK(A21),"", (C21*D21*F21*G21*H21*B21))</f>
+        <f t="shared" si="1"/>
         <v>4544.0999999999995</v>
       </c>
       <c r="K21">
@@ -2107,15 +2133,15 @@
       </c>
       <c r="M21">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N21">
         <f>IF(ISBLANK(#REF!), "", J21*K21*L21*M21/1000)</f>
-        <v>8.4823199999999981E-3</v>
+        <v>8.4611141999999997E-3</v>
       </c>
       <c r="O21">
-        <f t="shared" si="1"/>
-        <v>3.2561722285714278E-4</v>
+        <f t="shared" si="3"/>
+        <v>3.2532120719999994E-4</v>
       </c>
       <c r="Q21" s="2"/>
       <c r="R21" s="2" t="s">
@@ -2154,7 +2180,7 @@
         <v>28000</v>
       </c>
       <c r="D22" s="12">
-        <f>IF(ISBLANK(A22), "", VLOOKUP($A22, $Q$22:$Y$39, 2, FALSE))</f>
+        <f t="shared" si="0"/>
         <v>1.46</v>
       </c>
       <c r="E22" s="12">
@@ -2162,7 +2188,7 @@
         <v>0.5</v>
       </c>
       <c r="F22" s="12">
-        <f t="shared" si="0"/>
+        <f t="shared" si="2"/>
         <v>0.5</v>
       </c>
       <c r="G22" s="12">
@@ -2178,7 +2204,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="J22">
-        <f>IF(ISBLANK(A22),"", (C22*D22*F22*G22*H22*B22))</f>
+        <f t="shared" si="1"/>
         <v>4586.7359999999999</v>
       </c>
       <c r="K22">
@@ -2191,15 +2217,15 @@
       </c>
       <c r="M22">
         <f>IF(ISBLANK(#REF!),"",$R$6)</f>
-        <v>1.3333333333333333</v>
+        <v>1.33</v>
       </c>
       <c r="N22">
         <f>IF(ISBLANK(#REF!), "", J22*K22*L22*M22/1000)</f>
-        <v>8.5619071999999997E-3</v>
+        <v>8.5405024320000002E-3</v>
       </c>
       <c r="O22">
-        <f t="shared" si="1"/>
-        <v>3.2867239679999999E-4</v>
+        <f t="shared" si="3"/>
+        <v>3.2837360371200001E-4</v>
       </c>
       <c r="Q22" s="2" t="s">
         <v>22</v>
